--- a/price/price-fanline.xlsx
+++ b/price/price-fanline.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -502,7 +502,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Прайс-лист от 03.09.2026</t>
+          <t>Прайс-лист от 21.09.2026</t>
         </is>
       </c>
     </row>
@@ -523,403 +523,401 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Минимальный заказ 3 м³: меньше не возим, рейс не окупается. Возим только навалом, фасовки в мешках нет.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+          <t>Минимальный заказ навалом 3 м³: меньше не возим, рейс не окупается. Там, где рядом своя площадка, минимум ниже — от 1 м³: Балтым, Берёзовский, Верхняя Пышма, Екатеринбург, Монетный, Среднеуральск.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Чернозём, перегной и навоз возим только навалом. В мешках — почвогрунт, универсальная смесь, фрезерованный торф и опил, от 5 мешков.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Материал</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Цена за м³, ₽</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Примечание</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Чернозём</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>от 850</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>под грядки, газон, теплицу</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Перегной</t>
+          <t>Чернозём</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>от 1100</t>
+          <t>от 850</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>перепревший, под посадку</t>
+          <t>под грядки, газон, теплицу</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Навоз коровий</t>
+          <t>Перегной</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>от 900</t>
+          <t>от 1100</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>свежий и перепревший</t>
+          <t>перепревший, под посадку</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Навоз конский</t>
+          <t>Навоз коровий</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>от 1200</t>
+          <t>от 900</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>под тёплые грядки</t>
+          <t>свежий и перепревший</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Торф</t>
+          <t>Навоз конский</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>от 950</t>
+          <t>от 1200</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>низинный и верховой</t>
+          <t>под тёплые грядки</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Плодородный грунт</t>
+          <t>Торф</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>от 750</t>
+          <t>от 950</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>смесь под газон и отсыпку</t>
+          <t>низинный и верховой</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
+          <t>Плодородный грунт</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>от 750</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>смесь под газон и отсыпку</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
           <t>Торфогрунт</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>от 900</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>готовая смесь под рассаду</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Опилки</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>от 1000</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>мульча, подстилка, дорожки</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Доставка</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>от 76 ₽ за километр от базы, рейс считается туда и обратно, с подачей машины</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Базы разные: земля, торф и торфогрунт грузятся в Курганово (Полевской тракт), перегной и навоз — в Садовом. Плечо в таблице ниже дано для земли; по органике считаем от Садового.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>от 76 ₽ за километр от базы, рейс считается туда и обратно, с подачей машины</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Площадок три: Курганово (Полевской тракт) — земля, торф и торфогрунт; Садовый — перегной и навоз; Верхняя Пышма — опил, фасовка и весь ассортимент для Екатеринбурга и северного куста. Плечо в таблице ниже дано для земли от Курганово; по органике считаем от Садового, по опилу — от Верхней Пышмы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>Стоимость рейса не зависит от загрузки кузова, поэтому чем больше объём, тем дешевле выходит кубометр.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Куда</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Плечо, км</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Рейс, ₽</t>
         </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Курганово</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>1760</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Полевской тракт</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="C24" s="7" t="n">
-        <v>2520</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Горный Щит</t>
+          <t>Курганово</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>3280</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Северский</t>
+          <t>Полевской тракт</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>4040</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Полевской</t>
+          <t>Горный Щит</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>4800</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Северский</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>5560</v>
+        <v>4040</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Кашино</t>
+          <t>Полевской</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>5560</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Сысерть</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>6320</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Верхняя Сысерть</t>
+          <t>Кашино</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>6320</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Дегтярск</t>
+          <t>Черданцево</t>
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>6320</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Большой Исток</t>
+          <t>Сысерть</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>7080</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Патруши</t>
+          <t>Верхняя Сысерть</t>
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>7080</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Верхняя Пышма</t>
+          <t>Дегтярск</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>7840</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Берёзовский</t>
+          <t>Большой Исток</t>
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>7840</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Арамиль</t>
+          <t>Октябрьский</t>
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>7840</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Ревда</t>
+          <t>Патруши</t>
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>7840</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Челябинский тракт</t>
+          <t>Верхняя Пышма</t>
         </is>
       </c>
       <c r="B39" s="7" t="n">
@@ -932,122 +930,213 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Среднеуральск</t>
+          <t>Берёзовский</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>8600</v>
+        <v>7840</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Бобровский</t>
+          <t>Косулино</t>
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>8600</v>
+        <v>7840</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Верхнее Дуброво</t>
+          <t>Арамиль</t>
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>9360</v>
+        <v>7840</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Первоуральск</t>
+          <t>Ревда</t>
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>9360</v>
+        <v>7840</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Двуреченск</t>
+          <t>Челябинский тракт</t>
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>10120</v>
+        <v>7840</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Белоярский</t>
+          <t>Балтым</t>
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>10880</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Заречный</t>
+          <t>Среднеуральск</t>
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>10880</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Каменск-Уральский</t>
+          <t>Бобровский</t>
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>19240</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
+          <t>Верхнее Дуброво</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>9360</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Первоуральск</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>9360</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Монетный</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>10120</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Двуреченск</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>10120</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Белоярский</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>10880</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Заречный</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>10880</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Каменск-Уральский</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>19240</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
           <t>Нижний Тагил</t>
         </is>
       </c>
-      <c r="B48" s="7" t="n">
+      <c r="B55" s="7" t="n">
         <v>165</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C55" s="7" t="n">
         <v>26080</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Цены на материал ориентировочные, «от». Точную стоимость с доставкой называем по заявке в MAX, когда знаем объём, адрес и подъезд.</t>
         </is>

--- a/price/price-fanline.xlsx
+++ b/price/price-fanline.xlsx
@@ -502,7 +502,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Прайс-лист от 21.09.2026</t>
+          <t>Прайс-лист от 24.09.2026</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Чернозём, перегной и навоз возим только навалом. В мешках — почвогрунт, универсальная смесь, фрезерованный торф и опил, от 5 мешков.</t>
+          <t>Фасовка — по району Верхней Пышмы, примерно до 50 км от площадки: любой материал в мешках 20-25 л по 450 ₽; опил 50 л — 450 ₽, фрезерованный торф 40 л — 490 ₽, универсальная смесь 50 л — 550 ₽. От 5 мешков. Дальше — только навалом.</t>
         </is>
       </c>
     </row>
